--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_2_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_2_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M2" t="n">
         <v>13</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
         <v>7</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1531,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>2</v>
@@ -1923,10 +1923,10 @@
         <v>17</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2318,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2710,13 +2710,13 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
         <v>9</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>102</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X30" t="n">
         <v>25</v>
@@ -4488,7 +4488,7 @@
         <v>16</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -4880,7 +4880,7 @@
         <v>6</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         <v>27</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X39" t="n">
         <v>9</v>
@@ -5468,16 +5468,16 @@
         <v>23</v>
       </c>
       <c r="T41" t="n">
+        <v>7</v>
+      </c>
+      <c r="U41" t="n">
         <v>3</v>
       </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X41" t="n">
         <v>9</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>133</v>
       </c>
       <c r="T48" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X48" t="n">
         <v>46</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_2_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_2_EL.xlsx
@@ -674,10 +674,10 @@
         <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="O2" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="P3" t="n">
         <v>9</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>90.20</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,10 +1543,10 @@
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2327,14 +2327,14 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2719,14 +2719,14 @@
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y24" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -2915,14 +2915,14 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3839,14 +3839,14 @@
         <v>3</v>
       </c>
       <c r="X30" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="Y30" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4500,10 +4500,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -5088,14 +5088,14 @@
         <v>5</v>
       </c>
       <c r="X39" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y39" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5480,14 +5480,14 @@
         <v>3</v>
       </c>
       <c r="X41" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y43" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6264,14 +6264,14 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6460,10 +6460,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>8</v>
       </c>
       <c r="X48" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="Y48" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA48" t="n">
